--- a/Basics of Excel/01-Basic understanding.xlsx
+++ b/Basics of Excel/01-Basic understanding.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\Excel-for-Data-Analytics\Basics of Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517DB096-FB7A-48F5-826C-1BBC2B077DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,68 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Excel file = excel work book</t>
+  </si>
+  <si>
+    <t>inside the file there are some sheets called excel sheets or excel work sheets or spread sheets</t>
+  </si>
+  <si>
+    <t>Ribbons:</t>
+  </si>
+  <si>
+    <t>Tabs:</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>page laypout</t>
+  </si>
+  <si>
+    <t>data…</t>
+  </si>
+  <si>
+    <t>inside tabs there are different options called ribbons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups: </t>
+  </si>
+  <si>
+    <t>Separations inside tabs called groups</t>
+  </si>
+  <si>
+    <t>Menus:</t>
+  </si>
+  <si>
+    <t>inside groups there are menus options</t>
+  </si>
+  <si>
+    <t>Quick access tool bar</t>
+  </si>
+  <si>
+    <t>Bar having options used the most and we can add byself as well</t>
+  </si>
+  <si>
+    <t>Bilal</t>
+  </si>
+  <si>
+    <t>emplyee data</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +93,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +147,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +460,202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="79.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="79.7265625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="54.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="E1" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="7" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="4:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="4:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D13" s="2"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D14" s="2"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D15" s="2"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="4:13" x14ac:dyDescent="0.35">
+      <c r="D16" s="2"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="5"/>
+      <c r="D20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="I22" s="4"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="I30" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>